--- a/InputData/hydgn/BRHPF/BAU Recipient Hydrogen Pathway Fractions.xlsx
+++ b/InputData/hydgn/BRHPF/BAU Recipient Hydrogen Pathway Fractions.xlsx
@@ -1,39 +1,70 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\hydgn\RHPF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\hydgn\BRHPF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0C17625-A6F2-4CD5-93C4-F41CF1DD710F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F85B922-9F11-4FF4-A050-25C8627B5519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60630" yWindow="2445" windowWidth="23910" windowHeight="14415" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="BRHPF" sheetId="2" r:id="rId2"/>
+    <sheet name="Calcs" sheetId="3" r:id="rId2"/>
+    <sheet name="BRHPF" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="47">
   <si>
     <t>Source:</t>
   </si>
   <si>
-    <t>none needed</t>
-  </si>
-  <si>
     <t>Notes</t>
   </si>
   <si>
@@ -49,9 +80,6 @@
     <t>data.</t>
   </si>
   <si>
-    <t>For the U.S. model, it is configured to shift all pathways to</t>
-  </si>
-  <si>
     <t>electrolysis</t>
   </si>
   <si>
@@ -67,29 +95,122 @@
     <t>To type (below)  / From type (right)</t>
   </si>
   <si>
-    <t>Ensure that every column adds to 1.</t>
-  </si>
-  <si>
     <t>electrolysis with guaranteed clean electricity</t>
   </si>
   <si>
     <t>natural gas reforming with CCS</t>
   </si>
   <si>
-    <t>electrolysis that is guaranteed to be supplied by new clean electricity sources.</t>
-  </si>
-  <si>
     <t>hydrocarbon partial oxidation</t>
   </si>
   <si>
     <t>BRHPF BAU Recipient Hydrogen Pathway Fractions</t>
+  </si>
+  <si>
+    <t>Evolved Energy</t>
+  </si>
+  <si>
+    <t>2024 U.S. Annual Decarbonization Perspective</t>
+  </si>
+  <si>
+    <t>https://www.evolved.energy/us-adp-2024</t>
+  </si>
+  <si>
+    <t>Interactive Figure, H2 Production</t>
+  </si>
+  <si>
+    <t>were published before OBBBA and rescission of several green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hydrogen hubs' funding. </t>
+  </si>
+  <si>
+    <t>SMR</t>
+  </si>
+  <si>
+    <t>SMR w/ CCS</t>
+  </si>
+  <si>
+    <t>grid electrolysis</t>
+  </si>
+  <si>
+    <t>off-grid electrolysis</t>
+  </si>
+  <si>
+    <t>clean share</t>
+  </si>
+  <si>
+    <t>BNEF</t>
+  </si>
+  <si>
+    <t>https://efiling.energy.ca.gov/GetDocument.aspx?tn=265044</t>
+  </si>
+  <si>
+    <t>Clean share of total H2 production</t>
+  </si>
+  <si>
+    <t>Blue vs. Green Share</t>
+  </si>
+  <si>
+    <t>Clean Hydrogen production share</t>
+  </si>
+  <si>
+    <t>Blue vs. green shares</t>
+  </si>
+  <si>
+    <t>For the U.S. model, it is configured to shift total production towards</t>
+  </si>
+  <si>
+    <t>"current policies" forecasts published by Evolved Energy, which were</t>
+  </si>
+  <si>
+    <t>However we use blue- vs green-hydrogen production shares from</t>
+  </si>
+  <si>
+    <t>BNEF which we feel better reflect economic shifts in the forecasted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">price of electrolytic H2 vs CCS. </t>
+  </si>
+  <si>
+    <t>Blue</t>
+  </si>
+  <si>
+    <t>Green</t>
+  </si>
+  <si>
+    <t>assumption; lines up with recent publications from other orgs such as BNEF.</t>
+  </si>
+  <si>
+    <t>pg. 10</t>
+  </si>
+  <si>
+    <t>https://ekfs-quiet-skunk.euwest01.umbraco.io/media/kfjjd5fm/20241220-investment-pipeline-for-low-carbon-hydrogen-master-v2.pdf</t>
+  </si>
+  <si>
+    <t>US Clean Hydrogen Market Outlook / Investment Outlook for Low-Carbon Hydrogen</t>
+  </si>
+  <si>
+    <t>2025/24</t>
+  </si>
+  <si>
+    <t>grey</t>
+  </si>
+  <si>
+    <t>blue</t>
+  </si>
+  <si>
+    <t>green</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+  </numFmts>
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -105,13 +226,60 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -123,10 +291,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -141,9 +312,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="4">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 10" xfId="3" xr:uid="{DD09A7B5-2C5F-4BF5-88AC-392E992333BA}"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -421,60 +609,146 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="41.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B4" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="6">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B7" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B10" s="11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B12" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B14" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B15" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="7"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" s="1" t="s">
-        <v>13</v>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -484,224 +758,529 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D90A6AE8-3248-4806-9E8D-69A6DCDC1AC3}">
+  <dimension ref="A2:K22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C4">
+        <v>2024</v>
+      </c>
+      <c r="D4">
+        <v>2030</v>
+      </c>
+      <c r="E4">
+        <v>2035</v>
+      </c>
+      <c r="F4">
+        <v>2040</v>
+      </c>
+      <c r="G4">
+        <v>2045</v>
+      </c>
+      <c r="H4">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5">
+        <v>1.323</v>
+      </c>
+      <c r="D5">
+        <v>1.181</v>
+      </c>
+      <c r="E5">
+        <v>0.71</v>
+      </c>
+      <c r="F5">
+        <v>0.64500000000000002</v>
+      </c>
+      <c r="G5">
+        <v>0.67900000000000005</v>
+      </c>
+      <c r="H5">
+        <v>0.65400000000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6">
+        <v>0.253</v>
+      </c>
+      <c r="E6">
+        <v>1.02</v>
+      </c>
+      <c r="F6">
+        <v>1.2010000000000001</v>
+      </c>
+      <c r="G6">
+        <v>1.1479999999999999</v>
+      </c>
+      <c r="H6">
+        <v>1.167</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="F7">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G7">
+        <v>1.7000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="E8">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="F8">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="G8">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="H8">
+        <v>6.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C10" cm="1">
+        <f t="array" ref="C10:H10">C4:H4</f>
+        <v>2024</v>
+      </c>
+      <c r="D10">
+        <v>2030</v>
+      </c>
+      <c r="E10">
+        <v>2035</v>
+      </c>
+      <c r="F10">
+        <v>2040</v>
+      </c>
+      <c r="G10">
+        <v>2045</v>
+      </c>
+      <c r="H10">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="9">
+        <f>C5/SUM(C5:C8)</f>
+        <v>1</v>
+      </c>
+      <c r="D11" s="9">
+        <f t="shared" ref="D11:H11" si="0">D5/SUM(D5:D8)</f>
+        <v>0.78996655518394643</v>
+      </c>
+      <c r="E11" s="9">
+        <f t="shared" si="0"/>
+        <v>0.39313399778516062</v>
+      </c>
+      <c r="F11" s="9">
+        <f t="shared" si="0"/>
+        <v>0.33558792924037462</v>
+      </c>
+      <c r="G11" s="9">
+        <f t="shared" si="0"/>
+        <v>0.35643044619422576</v>
+      </c>
+      <c r="H11" s="9">
+        <f t="shared" si="0"/>
+        <v>0.34750265674814029</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="9" cm="1">
+        <f t="array" ref="C12">SUM(C6:C8/SUM(C5:C8))</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="9" cm="1">
+        <f t="array" ref="D12">SUM(D6:D8/SUM(D5:D8))</f>
+        <v>0.21003344481605349</v>
+      </c>
+      <c r="E12" s="9" cm="1">
+        <f t="array" ref="E12">SUM(E6:E8/SUM(E5:E8))</f>
+        <v>0.60686600221483944</v>
+      </c>
+      <c r="F12" s="9" cm="1">
+        <f t="array" ref="F12">SUM(F6:F8/SUM(F5:F8))</f>
+        <v>0.66441207075962538</v>
+      </c>
+      <c r="G12" s="9" cm="1">
+        <f t="array" ref="G12">SUM(G6:G8/SUM(G5:G8))</f>
+        <v>0.6435695538057743</v>
+      </c>
+      <c r="H12" s="9" cm="1">
+        <f t="array" ref="H12">SUM(H6:H8/SUM(H5:H8))</f>
+        <v>0.65249734325185971</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="15">
+        <f>H11</f>
+        <v>0.34750265674814029</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="15">
+        <f>H12*C17</f>
+        <v>0.52199787460148783</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="15">
+        <f>H12*C18</f>
+        <v>0.13049946865037196</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.26953125" customWidth="1"/>
-    <col min="2" max="6" width="16.54296875" style="3" customWidth="1"/>
-    <col min="7" max="8" width="16.453125" customWidth="1"/>
+    <col min="1" max="1" width="34.28515625" customWidth="1"/>
+    <col min="2" max="6" width="16.5703125" style="3" customWidth="1"/>
+    <col min="7" max="8" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="3">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="10">
+        <f>Calcs!C20</f>
+        <v>0.34750265674814029</v>
+      </c>
+      <c r="C3" s="10">
+        <f>B3</f>
+        <v>0.34750265674814029</v>
+      </c>
+      <c r="D3" s="10">
+        <f t="shared" ref="D3:H3" si="0">C3</f>
+        <v>0.34750265674814029</v>
+      </c>
+      <c r="E3" s="10">
+        <f t="shared" si="0"/>
+        <v>0.34750265674814029</v>
+      </c>
+      <c r="F3" s="10">
+        <f t="shared" si="0"/>
+        <v>0.34750265674814029</v>
+      </c>
+      <c r="G3" s="10">
+        <f t="shared" si="0"/>
+        <v>0.34750265674814029</v>
+      </c>
+      <c r="H3" s="10">
+        <f t="shared" si="0"/>
+        <v>0.34750265674814029</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="B4" s="3">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="B5" s="3">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="3">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="3">
-        <v>0</v>
-      </c>
-      <c r="C2" s="3">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3">
-        <v>0</v>
-      </c>
-      <c r="F2" s="3">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="3">
-        <v>0</v>
-      </c>
-      <c r="C3" s="3">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3">
-        <v>0</v>
-      </c>
-      <c r="E3" s="3">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="3">
-        <v>0</v>
-      </c>
-      <c r="C4" s="3">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3">
-        <v>0</v>
-      </c>
-      <c r="F4" s="3">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="3">
-        <v>0</v>
-      </c>
-      <c r="C5" s="3">
-        <v>0</v>
-      </c>
-      <c r="D5" s="3">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3">
-        <v>0</v>
-      </c>
-      <c r="F5" s="3">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="3">
-        <v>0</v>
-      </c>
-      <c r="C6" s="3">
-        <v>0</v>
-      </c>
-      <c r="D6" s="3">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="3">
-        <v>1</v>
-      </c>
-      <c r="C7" s="3">
-        <v>1</v>
-      </c>
-      <c r="D7" s="3">
-        <v>1</v>
-      </c>
-      <c r="E7" s="3">
-        <v>1</v>
-      </c>
-      <c r="F7" s="3">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B7" s="10">
+        <f>Calcs!C22</f>
+        <v>0.13049946865037196</v>
+      </c>
+      <c r="C7" s="10">
+        <f t="shared" ref="C7:H7" si="1">B7</f>
+        <v>0.13049946865037196</v>
+      </c>
+      <c r="D7" s="10">
+        <f t="shared" si="1"/>
+        <v>0.13049946865037196</v>
+      </c>
+      <c r="E7" s="10">
+        <f t="shared" si="1"/>
+        <v>0.13049946865037196</v>
+      </c>
+      <c r="F7" s="10">
+        <f t="shared" si="1"/>
+        <v>0.13049946865037196</v>
+      </c>
+      <c r="G7" s="10">
+        <f t="shared" si="1"/>
+        <v>0.13049946865037196</v>
+      </c>
+      <c r="H7" s="10">
+        <f t="shared" si="1"/>
+        <v>0.13049946865037196</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="3">
-        <v>0</v>
-      </c>
-      <c r="C8" s="3">
-        <v>0</v>
-      </c>
-      <c r="D8" s="3">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="B8" s="10">
+        <f>Calcs!C21</f>
+        <v>0.52199787460148783</v>
+      </c>
+      <c r="C8" s="10">
+        <f t="shared" ref="C8:H8" si="2">B8</f>
+        <v>0.52199787460148783</v>
+      </c>
+      <c r="D8" s="10">
+        <f t="shared" si="2"/>
+        <v>0.52199787460148783</v>
+      </c>
+      <c r="E8" s="10">
+        <f t="shared" si="2"/>
+        <v>0.52199787460148783</v>
+      </c>
+      <c r="F8" s="10">
+        <f t="shared" si="2"/>
+        <v>0.52199787460148783</v>
+      </c>
+      <c r="G8" s="10">
+        <f t="shared" si="2"/>
+        <v>0.52199787460148783</v>
+      </c>
+      <c r="H8" s="10">
+        <f t="shared" si="2"/>
+        <v>0.52199787460148783</v>
       </c>
     </row>
   </sheetData>
